--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -17168,12 +17168,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -17198,12 +17198,12 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N91" t="n">
@@ -17212,6 +17212,9 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
+      <c r="P91" t="n">
+        <v>0</v>
+      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -17220,66 +17223,457 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP91" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT91" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU91" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV91" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA91" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB91" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC91" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO92" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP92" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT92" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU92" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV92" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA92" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB92" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC92" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N93" t="n">
+        <v>0</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0</v>
+      </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO93" t="inlineStr">
+        <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP91" t="inlineStr">
+      <c r="AP93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR91" t="inlineStr">
+      <c r="AR93" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS91" t="inlineStr"/>
-      <c r="AT91" t="n">
+      <c r="AS93" t="inlineStr"/>
+      <c r="AT93" t="n">
         <v>0</v>
       </c>
-      <c r="AU91" t="inlineStr">
+      <c r="AU93" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV91" t="inlineStr">
+      <c r="AV93" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW91" t="inlineStr">
+      <c r="AW93" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX91" t="inlineStr">
+      <c r="AX93" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY91" t="inlineStr">
+      <c r="AY93" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ91" t="inlineStr">
+      <c r="AZ93" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA91" t="inlineStr">
+      <c r="BA93" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB91" t="inlineStr">
+      <c r="BB93" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC91" t="inlineStr">
+      <c r="BC93" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -17401,7 +17795,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -17411,7 +17805,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
     </row>
     <row r="11">
@@ -17431,7 +17825,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -17679,6 +17679,400 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N94" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" t="n">
+        <v>1</v>
+      </c>
+      <c r="P94" t="n">
+        <v>1</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP94" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ94" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT94" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU94" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV94" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA94" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB94" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC94" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N95" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1</v>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X95" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD95" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE95" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF95" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG95" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH95" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM95" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN95" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP95" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ95" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS95" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT95" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU95" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV95" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA95" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB95" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC95" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17712,7 +18106,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -17795,7 +18189,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -17805,7 +18199,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11">
@@ -17825,7 +18219,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -17857,7 +18251,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -15447,12 +15447,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -15525,42 +15525,42 @@
       </c>
       <c r="AV82" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA82" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB82" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC82" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15592,12 +15592,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -15622,7 +15622,7 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
@@ -15631,93 +15631,81 @@
         </is>
       </c>
       <c r="N83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O83" t="n">
-        <v>3</v>
-      </c>
-      <c r="P83" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>0.05079797265291142</v>
+        <v>0</v>
       </c>
       <c r="S83" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA83" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ83" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS83" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR83" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS83" t="inlineStr"/>
       <c r="AT83" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU83" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV83" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA83" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB83" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC83" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15744,7 +15732,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -15796,98 +15784,18 @@
       <c r="P84" t="n">
         <v>3</v>
       </c>
-      <c r="U84" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V84" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W84" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X84" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y84" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R84" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD84" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE84" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF84" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG84" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH84" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI84" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM84" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN84" t="b">
-        <v>1</v>
       </c>
       <c r="AO84" t="inlineStr">
         <is>
@@ -15981,7 +15889,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -16016,7 +15924,7 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
@@ -16025,26 +15933,106 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O85" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P85" t="n">
-        <v>5</v>
-      </c>
-      <c r="R85" t="n">
-        <v>0.08466328775485238</v>
-      </c>
-      <c r="S85" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>3</v>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X85" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD85" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE85" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF85" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG85" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH85" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI85" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM85" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN85" t="b">
+        <v>1</v>
       </c>
       <c r="AO85" t="inlineStr">
         <is>
@@ -16138,7 +16126,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -16190,98 +16178,18 @@
       <c r="P86" t="n">
         <v>5</v>
       </c>
-      <c r="U86" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R86" t="n">
+        <v>0.08466328775485238</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD86" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG86" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN86" t="b">
-        <v>1</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -16375,7 +16283,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -16410,7 +16318,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M87" t="inlineStr">
@@ -16419,26 +16327,106 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O87" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0</v>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>5</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN87" t="b">
+        <v>1</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
@@ -16532,7 +16520,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -16584,98 +16572,18 @@
       <c r="P88" t="n">
         <v>0</v>
       </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V88" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W88" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X88" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y88" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD88" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE88" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF88" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG88" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH88" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI88" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM88" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN88" t="b">
-        <v>1</v>
       </c>
       <c r="AO88" t="inlineStr">
         <is>
@@ -16769,7 +16677,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -16804,7 +16712,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -16813,26 +16721,106 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P89" t="n">
-        <v>2</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0.03386531510194095</v>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>0</v>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
+        <v>1</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -16926,7 +16914,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -16978,98 +16966,18 @@
       <c r="P90" t="n">
         <v>2</v>
       </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R90" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN90" t="b">
-        <v>1</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
@@ -17163,7 +17071,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -17198,7 +17106,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -17207,26 +17115,106 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O91" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
-      </c>
-      <c r="R91" t="n">
-        <v>0</v>
-      </c>
-      <c r="S91" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
+        <v>2</v>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X91" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD91" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE91" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG91" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH91" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI91" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM91" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN91" t="b">
+        <v>1</v>
       </c>
       <c r="AO91" t="inlineStr">
         <is>
@@ -17320,7 +17308,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -17372,98 +17360,18 @@
       <c r="P92" t="n">
         <v>0</v>
       </c>
-      <c r="U92" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V92" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W92" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X92" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y92" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R92" t="n">
+        <v>0</v>
+      </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD92" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE92" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF92" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG92" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH92" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ92" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK92" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM92" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN92" t="b">
-        <v>1</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
@@ -17557,17 +17465,17 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -17592,12 +17500,12 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N93" t="n">
@@ -17606,76 +17514,168 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="R93" t="n">
+      <c r="P93" t="n">
         <v>0</v>
       </c>
-      <c r="S93" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X93" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD93" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE93" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF93" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG93" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH93" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ93" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK93" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM93" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN93" t="b">
+        <v>1</v>
       </c>
       <c r="AO93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR93" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS93" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ93" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS93" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU93" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -17707,12 +17707,12 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -17737,7 +17737,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -17746,93 +17746,81 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O94" t="n">
-        <v>1</v>
-      </c>
-      <c r="P94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>0.01693265755097047</v>
+        <v>0</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA94" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO94" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ94" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS94" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR94" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS94" t="inlineStr"/>
       <c r="AT94" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU94" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV94" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA94" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB94" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC94" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -17859,7 +17847,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -17911,98 +17899,18 @@
       <c r="P95" t="n">
         <v>1</v>
       </c>
-      <c r="U95" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="V95" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_MURINE_TYPHUS</t>
-        </is>
-      </c>
-      <c r="W95" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X95" t="inlineStr">
-        <is>
-          <t>Murine Typhus</t>
-        </is>
-      </c>
-      <c r="Y95" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R95" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD95" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE95" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF95" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG95" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH95" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI95" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM95" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN95" t="b">
-        <v>1</v>
       </c>
       <c r="AO95" t="inlineStr">
         <is>
@@ -18068,6 +17976,637 @@
         </is>
       </c>
       <c r="BC95" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N96" t="n">
+        <v>1</v>
+      </c>
+      <c r="O96" t="n">
+        <v>1</v>
+      </c>
+      <c r="P96" t="n">
+        <v>1</v>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X96" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD96" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE96" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF96" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG96" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH96" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM96" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN96" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP96" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ96" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS96" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT96" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU96" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV96" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA96" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB96" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC96" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N97" t="n">
+        <v>2</v>
+      </c>
+      <c r="O97" t="n">
+        <v>2</v>
+      </c>
+      <c r="P97" t="n">
+        <v>2</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP97" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ97" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT97" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU97" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV97" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA97" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB97" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC97" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N98" t="n">
+        <v>2</v>
+      </c>
+      <c r="O98" t="n">
+        <v>2</v>
+      </c>
+      <c r="P98" t="n">
+        <v>2</v>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X98" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD98" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE98" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF98" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG98" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH98" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM98" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN98" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP98" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ98" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT98" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU98" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV98" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA98" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB98" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC98" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -18106,7 +18645,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -18189,7 +18728,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="10">
@@ -18199,7 +18738,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
     </row>
     <row r="11">
@@ -18219,7 +18758,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="13">
@@ -18251,7 +18790,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -18612,6 +18612,545 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT99" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA99" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB99" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC99" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>0</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0</v>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X100" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD100" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE100" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF100" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG100" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH100" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM100" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN100" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT100" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -18645,7 +19184,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -18728,7 +19267,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -18738,7 +19277,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -18758,7 +19297,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -17746,13 +17746,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -19329,7 +19329,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -773,6 +773,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -918,6 +923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1066,6 +1076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2787,6 +2802,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2932,6 +2952,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4653,6 +4678,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4798,6 +4828,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5340,6 +5375,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7061,6 +7101,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO36" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7206,6 +7251,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7351,6 +7401,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO38" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9072,6 +9127,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9217,6 +9277,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9362,6 +9427,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11477,6 +11547,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO60" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11622,6 +11697,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO61" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -11767,6 +11847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO62" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13488,6 +13573,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO71" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13633,6 +13723,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO72" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13778,6 +13873,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO73" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15499,6 +15599,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15644,6 +15749,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO83" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17759,6 +17869,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -19034,118 +19149,517 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>4</v>
+      </c>
+      <c r="O101" t="n">
+        <v>4</v>
+      </c>
+      <c r="P101" t="n">
+        <v>4</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.0677306302038819</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT101" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA101" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB101" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC101" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>4</v>
+      </c>
+      <c r="O102" t="n">
+        <v>4</v>
+      </c>
+      <c r="P102" t="n">
+        <v>4</v>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X102" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD102" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE102" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF102" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG102" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH102" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM102" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN102" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ102" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT102" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
           <t>KR</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="G103" t="inlineStr">
         <is>
           <t>South Korea</t>
         </is>
       </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>D169</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Endemic typhus fever</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
         <is>
           <t>地方性斑疹伤寒</t>
         </is>
       </c>
-      <c r="K101" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L101" t="inlineStr">
+      <c r="L103" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
+      <c r="M103" t="inlineStr">
         <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="N101" t="n">
+      <c r="N103" t="n">
         <v>0</v>
       </c>
-      <c r="O101" t="n">
+      <c r="O103" t="n">
         <v>0</v>
       </c>
-      <c r="R101" t="n">
+      <c r="R103" t="n">
         <v>0</v>
       </c>
-      <c r="S101" t="inlineStr">
+      <c r="S103" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO101" t="inlineStr">
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP101" t="inlineStr">
+      <c r="AP103" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR101" t="inlineStr">
+      <c r="AR103" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS101" t="inlineStr"/>
-      <c r="AT101" t="n">
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
         <v>0</v>
       </c>
-      <c r="AU101" t="inlineStr">
+      <c r="AU103" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV101" t="inlineStr">
+      <c r="AV103" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW101" t="inlineStr">
+      <c r="AW103" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX101" t="inlineStr">
+      <c r="AX103" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY101" t="inlineStr">
+      <c r="AY103" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ101" t="inlineStr">
+      <c r="AZ103" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA101" t="inlineStr">
+      <c r="BA103" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB101" t="inlineStr">
+      <c r="BB103" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC101" t="inlineStr">
+      <c r="BC103" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -19267,7 +19781,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10">
@@ -19277,7 +19791,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="11">
@@ -19297,7 +19811,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
@@ -19329,7 +19843,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -19665,6 +19665,400 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>1</v>
+      </c>
+      <c r="O104" t="n">
+        <v>1</v>
+      </c>
+      <c r="P104" t="n">
+        <v>1</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ104" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT104" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="n">
+        <v>1</v>
+      </c>
+      <c r="P105" t="n">
+        <v>1</v>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X105" t="inlineStr">
+        <is>
+          <t>Murine Typhus</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD105" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE105" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF105" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG105" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH105" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ105" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM105" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN105" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ105" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_MURINE_TYPHUS; SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT105" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19698,7 +20092,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -19781,7 +20175,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10">
@@ -19791,7 +20185,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -19811,7 +20205,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="13">
@@ -19843,7 +20237,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d169/2026-2029.xlsx
+++ b/diseases/d169/2026-2029.xlsx
@@ -9819,6 +9819,153 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>endemic-typhus-fever</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>D169</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Endemic typhus fever</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>地方性斑疹伤寒</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0</v>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AO66" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP66" t="inlineStr">
+        <is>
+          <t>published_series</t>
+        </is>
+      </c>
+      <c r="AS66" t="inlineStr">
+        <is>
+          <t>SER_SG_HIST_MURINE_TYPHUS</t>
+        </is>
+      </c>
+      <c r="AT66" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV66" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA66" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB66" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC66" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9852,7 +9999,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-11</t>
         </is>
       </c>
     </row>
@@ -9935,7 +10082,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
@@ -9945,7 +10092,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="11">
